--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/synhtesis_yingshi.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/synhtesis_yingshi.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -656,7 +656,7 @@
     <t>1#50030101#1|1#50030201#1</t>
   </si>
   <si>
-    <t>1#50030005#1|1#50030001#1</t>
+    <t>1#1253000599#1|1#1253000199#1</t>
   </si>
   <si>
     <t>10010002#4000</t>
@@ -704,7 +704,7 @@
     <t>2#4#0#2#0#1|2#4#0#1#0#1</t>
   </si>
   <si>
-    <t>1#50030008#1|1#50030005#1|1#50030001#1</t>
+    <t>1#50030008#1|1#1253000599#1|1#1253000199#1</t>
   </si>
   <si>
     <t>10010002#60000</t>
